--- a/templates/employee_vacations_mark_template.xlsx
+++ b/templates/employee_vacations_mark_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA807E0A-A7C2-451A-8DBE-47FBADC4BAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C9FC4F-91E8-4CBD-9013-5F93D2F45A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76E59773-EC53-4AF5-A7A0-44CFC0834E71}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
   <si>
     <t>1º</t>
   </si>
@@ -64,13 +64,19 @@
   </si>
   <si>
     <t>Data:</t>
+  </si>
+  <si>
+    <t>Nome do Funcionário(a)</t>
+  </si>
+  <si>
+    <t>Nº Interno</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +103,21 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -118,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -212,59 +233,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -606,336 +653,314 @@
     <col min="20" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+    </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="4"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="21"/>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="8"/>
+      <c r="B10" s="2"/>
+      <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="12" t="s">
+      <c r="I11" s="5"/>
+      <c r="J11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="23"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="15"/>
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="12" t="s">
+      <c r="I13" s="5"/>
+      <c r="J13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="23"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="15"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="8"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="12" t="s">
+      <c r="I15" s="5"/>
+      <c r="J15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="23"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="15"/>
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="13"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="8"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="3"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="12" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="8"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="3"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="8"/>
+      <c r="B18" s="2"/>
+      <c r="R18" s="3"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="17" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="O19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="8"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="3"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="8"/>
+      <c r="B20" s="2"/>
+      <c r="R20" s="3"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="17" t="s">
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="O21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="8"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="3"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="20"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="G21:M21"/>

--- a/templates/employee_vacations_mark_template.xlsx
+++ b/templates/employee_vacations_mark_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C9FC4F-91E8-4CBD-9013-5F93D2F45A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AF0DFB-351C-4638-A24F-C2CA5C50C3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{76E59773-EC53-4AF5-A7A0-44CFC0834E71}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="14">
   <si>
     <t>1º</t>
   </si>
@@ -70,38 +70,25 @@
   </si>
   <si>
     <t>Nº Interno</t>
+  </si>
+  <si>
+    <t>Marcação de Férias</t>
+  </si>
+  <si>
+    <t>PEDIDO DE ALTERAÇÃO DE FÉRIAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -113,10 +100,11 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="20"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -252,66 +240,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -329,6 +311,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>154850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo_Marcação _de_Férias">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF27957B-B84A-45F4-BA1B-033FBECFDFCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="295275" y="196850"/>
+          <a:ext cx="568325" cy="720000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -628,339 +665,557 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C3D2BA-B347-4D60-91C1-F1F42FA53BBF}">
-  <dimension ref="A7:S22"/>
+  <dimension ref="A3:S37"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="3.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="2.85546875" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" customWidth="1"/>
-    <col min="9" max="9" width="4.28515625" customWidth="1"/>
-    <col min="10" max="10" width="2.85546875" customWidth="1"/>
-    <col min="11" max="11" width="4.28515625" customWidth="1"/>
-    <col min="12" max="12" width="2.85546875" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" customWidth="1"/>
-    <col min="14" max="14" width="1.42578125" customWidth="1"/>
-    <col min="15" max="15" width="5.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.28515625" customWidth="1"/>
-    <col min="17" max="17" width="7.85546875" customWidth="1"/>
-    <col min="18" max="18" width="1.42578125" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="3.5703125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="2.85546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="2.85546875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="2.85546875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="4.28515625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="2.85546875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="9.28515625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="7.85546875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="1.42578125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="4" customWidth="1"/>
     <col min="20" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+    </row>
     <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="25" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="21"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:19" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="R10" s="3"/>
+      <c r="B10" s="9"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="22" t="s">
+      <c r="I11" s="19"/>
+      <c r="J11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="19"/>
+      <c r="L11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="1"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="11"/>
     </row>
     <row r="12" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="3"/>
+      <c r="B12" s="9"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="22" t="s">
+      <c r="I13" s="19"/>
+      <c r="J13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="1"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="11"/>
     </row>
     <row r="14" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="3"/>
+      <c r="B14" s="9"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="22" t="s">
+      <c r="I15" s="19"/>
+      <c r="J15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="19"/>
+      <c r="L15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="19"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="1"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="11"/>
     </row>
     <row r="16" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="3"/>
+      <c r="B16" s="9"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="22" t="s">
+      <c r="B17" s="9"/>
+      <c r="O17" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="3"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="21">
+        <f>IFERROR(SUM(Q11,Q13,Q15),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="R18" s="3"/>
+      <c r="B18" s="9"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="O19" s="9" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="O19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="3"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-      <c r="R20" s="3"/>
+      <c r="B20" s="9"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="O21" s="9" t="s">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="O21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="3"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="10"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="12"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="17"/>
+    </row>
+    <row r="23" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="8"/>
+    </row>
+    <row r="25" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="9"/>
+      <c r="R25" s="10"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B26" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="19"/>
+      <c r="F26" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="19"/>
+      <c r="H26" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="19"/>
+      <c r="J26" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="19"/>
+      <c r="L26" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M26" s="19"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="12"/>
+    </row>
+    <row r="27" spans="2:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="9"/>
+      <c r="R27" s="10"/>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B28" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="19"/>
+      <c r="F28" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="19"/>
+      <c r="H28" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="19"/>
+      <c r="J28" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="19"/>
+      <c r="L28" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M28" s="19"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="12"/>
+    </row>
+    <row r="29" spans="2:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="9"/>
+      <c r="R29" s="10"/>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B30" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="19"/>
+      <c r="F30" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="19"/>
+      <c r="J30" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K30" s="19"/>
+      <c r="L30" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M30" s="19"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="12"/>
+    </row>
+    <row r="31" spans="2:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="9"/>
+      <c r="R31" s="10"/>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B32" s="9"/>
+      <c r="O32" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="21">
+        <f>IFERROR(SUM(Q26,Q28,Q30),"")</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="10"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B33" s="9"/>
+      <c r="R33" s="10"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B34" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="O34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="10"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B35" s="9"/>
+      <c r="R35" s="10"/>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B36" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="O36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="10"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B37" s="15"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="26">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="G36:M36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="B3:R4"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G34:M34"/>
+    <mergeCell ref="P34:Q34"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:O7"/>
     <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="B24:R24"/>
+    <mergeCell ref="O26:P26"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="P19:Q19"/>
     <mergeCell ref="G21:M21"/>
@@ -975,5 +1230,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>